--- a/水库项目出表/Template/土地调查成果确认表.xlsx
+++ b/水库项目出表/Template/土地调查成果确认表.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sunchuanhong\Local\code\水库项目出表\Template\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="600" yWindow="105" windowWidth="19395" windowHeight="7605"/>
+    <workbookView xWindow="600" yWindow="110" windowWidth="19400" windowHeight="7610"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,9 +34,6 @@
     <t>地块编号</t>
   </si>
   <si>
-    <t>土地面积（亩）</t>
-  </si>
-  <si>
     <t>户主签字确认</t>
   </si>
   <si>
@@ -63,17 +65,21 @@
   </si>
   <si>
     <t xml:space="preserve"> #区县名#   #乡镇名#   #村名#  #组名#       </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>土地面积（#单位#）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,11 +214,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -254,7 +268,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -286,9 +300,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -320,6 +335,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -495,16 +511,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="13.625" customWidth="1"/>
-    <col min="3" max="3" width="19.375" style="8" customWidth="1"/>
-    <col min="4" max="9" width="13.625" customWidth="1"/>
+    <col min="1" max="2" width="13.6328125" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" style="8" customWidth="1"/>
+    <col min="4" max="9" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1">
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -517,9 +533,9 @@
       <c r="H1" s="9"/>
       <c r="I1" s="9"/>
     </row>
-    <row r="2" spans="1:9" ht="14.25">
+    <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -530,7 +546,7 @@
       <c r="H2" s="10"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
@@ -541,62 +557,62 @@
         <v>3</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
       <c r="H3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="11" t="s">
-        <v>6</v>
-      </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="11"/>
       <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="11"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="7"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="7"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>

--- a/水库项目出表/Template/土地调查成果确认表.xlsx
+++ b/水库项目出表/Template/土地调查成果确认表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>#水库名#工程耕（园、林）地土地调查成果确认表</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -69,6 +69,31 @@
   </si>
   <si>
     <t>土地面积（#单位#）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>坑塘水面</t>
+  </si>
+  <si>
+    <t>农村道路</t>
+  </si>
+  <si>
+    <t>沟渠</t>
+  </si>
+  <si>
+    <t>设施农用地</t>
+  </si>
+  <si>
+    <t>田坎</t>
+  </si>
+  <si>
+    <t>建设用地</t>
+  </si>
+  <si>
+    <t>未利用地</t>
+  </si>
+  <si>
+    <t>水库水面</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -139,7 +164,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -162,13 +187,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -196,6 +256,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -207,6 +273,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -512,67 +590,91 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13.6328125" customWidth="1"/>
     <col min="3" max="3" width="19.36328125" style="8" customWidth="1"/>
-    <col min="4" max="9" width="13.6328125" customWidth="1"/>
+    <col min="4" max="17" width="13.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
     </row>
-    <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="1"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="11" t="s">
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="Q3" s="15" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="11"/>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="13"/>
       <c r="D4" s="2" t="s">
         <v>6</v>
       </c>
@@ -582,13 +684,37 @@
       <c r="F4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
@@ -596,14 +722,22 @@
       <c r="C5" s="7"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>12</v>
       </c>
@@ -611,23 +745,33 @@
       <c r="C6" s="7"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:H2"/>
+  <mergeCells count="10">
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A2:P2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="D3:O3"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
